--- a/docsbug-reports.xlsx
+++ b/docsbug-reports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFB4CE5-24CE-49A0-B7F5-3EA9F40A02B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A8CCB6-D06D-45AD-ABC1-C55EAAE385FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Баг репорты" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="74">
   <si>
     <t>ID</t>
   </si>
@@ -184,18 +184,6 @@
     <t>200 OK, бронь создана с невалидными датами</t>
   </si>
   <si>
-    <t>Сервер возвращает 201 Created при повторном удалении уже удаленной брони</t>
-  </si>
-  <si>
-    <t>1. Удалить бронь через DELETE /booking/{id}</t>
-  </si>
-  <si>
-    <t>404 Not Found или 405 Method Not Allowed</t>
-  </si>
-  <si>
-    <t>201 Created, бронь "удалена" повторно</t>
-  </si>
-  <si>
     <t>Сервер возвращает 405 Method Not Allowed вместо 404 Not Found при удалении несуществующей брони</t>
   </si>
   <si>
@@ -245,9 +233,6 @@
   </si>
   <si>
     <t>8_booking - Отправить дату в неверном формате</t>
-  </si>
-  <si>
-    <t>удаление уже удаленного</t>
   </si>
   <si>
     <t>удаление_bookingid с невалидным ID</t>
@@ -280,9 +265,19 @@
 </t>
   </si>
   <si>
-    <t>В ходе тестирования я обнаружил 13 багов, из которых 3 — критических. Самое опасное — это уязвимость в /auth, где сервер выдает токен невалидным пользователям.
- Также я нашел системную проблему с валидацией входных данных: сервер создает брони с пустыми полями, отрицательными ценами и некорректными датами.
- Все баги зафиксированы в отчете с шагами воспроизведения и ожидаемым/фактическим результатом</t>
+    <t>В ходе тестирования Restful-Booker API обнаружено 12 багов: 3 Critical, 8 High, 1 Medium.
+Критические баги:
+AUTH-4: сервер выдаёт токен при невалидной паре логин/пароль.
+AUTH-5: сервер выдаёт токен при пустом теле запроса.
+BOOKING-7: сервер создаёт бронь с checkin &gt; checkout.
+Основные проблемы:
+Эндпоинт /auth не валидирует входные данные → критическая уязвимость безопасности.
+Эндпоинт /booking не проверяет обязательные поля (firstname, lastname, totalprice, bookingdates) → создаются мусорные брони.
+Эндпоинт /booking не проверяет бизнес-логику (отрицательная цена, некорректные даты) → нарушение целостности данных.
+При отсутствии totalprice и bookingdates сервер возвращает 500 вместо 400 → слабая обработка исключений.
+Особенности сервера (не баги):
+Повторное удаление и запросы с невалидным ID возвращают 405 вместо 404 — учтено в тестах.
+Рекомендация: в первую очередь исправить /auth (безопасность) и валидацию /booking (целостность данных).</t>
   </si>
 </sst>
 </file>
@@ -720,422 +715,433 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="65" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="93.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="96" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.21875" style="11" customWidth="1"/>
-    <col min="5" max="5" width="91.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="59.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="91.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="59.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>20</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>23</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>20</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="H10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="11" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="B11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>20</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="D12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="D13" s="10" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1159,7 +1165,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1168,7 +1174,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>20</v>
@@ -1177,15 +1183,15 @@
         <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B3" s="7">
         <v>2</v>
@@ -1202,7 +1208,7 @@
     </row>
     <row r="4" spans="1:5" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B4" s="7">
         <v>1</v>
@@ -1219,7 +1225,7 @@
     </row>
     <row r="5" spans="1:5" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B5" s="7">
         <v>0</v>
@@ -1236,7 +1242,7 @@
     </row>
     <row r="6" spans="1:5" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B6" s="8">
         <f>SUM(B3:B5)</f>
@@ -1257,7 +1263,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -1308,9 +1314,9 @@
     <col min="1" max="1" width="144.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="360" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
